--- a/emergency_report_forms/019_disaster_recovery_plan_form--emergency_report_forms.xlsx
+++ b/emergency_report_forms/019_disaster_recovery_plan_form--emergency_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -920,7 +920,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Services Restored</t>
+          <t>Services Restored Name</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -961,12 +961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>personnel_involved</t>
+          <t>personnel_involved_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Personnel Involved</t>
+          <t>Personnel Involved 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>restoration_time</t>
+          <t>restoration_time_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Restoration Time</t>
+          <t>Restoration Time 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>personnel_contacts</t>
+          <t>personnel_contacts_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Personnel Contacts</t>
+          <t>Personnel Contacts 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>recovery_plan_status</t>
+          <t>recovery_plan_status_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Recovery Plan Status</t>
+          <t>Recovery Plan Status 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>additional_notes</t>
+          <t>additional_notes_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Additional Notes</t>
+          <t>Additional Notes 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>services_restored</t>
+          <t>services_restored_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Services Restored</t>
+          <t>Services Restored 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>personnel_involved_choices</t>
+          <t>personnel_involved_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1385,7 +1385,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>personnel_involved_choices</t>
+          <t>personnel_involved_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1402,7 +1402,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>personnel_contacts_choices</t>
+          <t>personnel_contacts_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>personnel_contacts_choices</t>
+          <t>personnel_contacts_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1436,7 +1436,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>recovery_plan_status_choices</t>
+          <t>recovery_plan_status_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1453,7 +1453,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>recovery_plan_status_choices</t>
+          <t>recovery_plan_status_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1470,7 +1470,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>services_restored_choices</t>
+          <t>services_restored_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1487,7 +1487,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>services_restored_choices</t>
+          <t>services_restored_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
